--- a/informes_data/Euroleague/2025-26/Regular_Season/individual/NP_play_by_play_EL_29_R3.xlsx
+++ b/informes_data/Euroleague/2025-26/Regular_Season/individual/NP_play_by_play_EL_29_R3.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>4.604</v>
+        <v>3.1549</v>
       </c>
       <c r="E2" t="n">
-        <v>3.6405</v>
+        <v>2.2251</v>
       </c>
       <c r="F2" t="n">
-        <v>0.9635</v>
+        <v>0.9298999999999999</v>
       </c>
       <c r="G2" t="n">
         <v>2.2752</v>
@@ -610,13 +610,13 @@
         <v>1.3917</v>
       </c>
       <c r="S2" t="n">
-        <v>2.0968</v>
+        <v>0.6477000000000001</v>
       </c>
       <c r="T2" t="n">
-        <v>2.0603</v>
+        <v>0.6449</v>
       </c>
       <c r="U2" t="n">
-        <v>0.0365</v>
+        <v>0.0029</v>
       </c>
       <c r="V2" t="n">
         <v>0</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>1.1259</v>
+        <v>0.9311</v>
       </c>
       <c r="E3" t="n">
-        <v>3.0193</v>
+        <v>2.8581</v>
       </c>
       <c r="F3" t="n">
-        <v>-1.8934</v>
+        <v>-1.927</v>
       </c>
       <c r="G3" t="n">
         <v>-1.2463</v>
@@ -688,13 +688,13 @@
         <v>1.8556</v>
       </c>
       <c r="S3" t="n">
-        <v>0.06809999999999999</v>
+        <v>-0.1267</v>
       </c>
       <c r="T3" t="n">
-        <v>0.3462</v>
+        <v>0.1849</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.2781</v>
+        <v>-0.3117</v>
       </c>
       <c r="V3" t="n">
         <v>1.6083</v>
@@ -709,7 +709,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>K. BALDWIN</t>
+          <t>J. HOLLATZ</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>-1.4703</v>
+        <v>-1.2006</v>
       </c>
       <c r="E4" t="n">
-        <v>0.1144</v>
+        <v>-1.0579</v>
       </c>
       <c r="F4" t="n">
-        <v>-1.5847</v>
+        <v>-0.1427</v>
       </c>
       <c r="G4" t="n">
-        <v>-1.0229</v>
+        <v>-1.4659</v>
       </c>
       <c r="H4" t="n">
-        <v>0.2185</v>
+        <v>-0.9975000000000001</v>
       </c>
       <c r="I4" t="n">
-        <v>-1.2413</v>
+        <v>-0.4684</v>
       </c>
       <c r="J4" t="n">
-        <v>0.346</v>
+        <v>-0.4723</v>
       </c>
       <c r="K4" t="n">
-        <v>0.2724</v>
+        <v>-0.9005</v>
       </c>
       <c r="L4" t="n">
-        <v>0.0736</v>
+        <v>0.4282</v>
       </c>
       <c r="M4" t="n">
-        <v>-1.3688</v>
+        <v>-0.9937</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.0539</v>
+        <v>-0.097</v>
       </c>
       <c r="O4" t="n">
-        <v>-1.3149</v>
+        <v>-0.8966</v>
       </c>
       <c r="P4" t="n">
-        <v>0</v>
+        <v>1.3917</v>
       </c>
       <c r="Q4" t="n">
         <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>0</v>
+        <v>1.3917</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.0532</v>
+        <v>-1.1264</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.3734</v>
+        <v>-0.5856</v>
       </c>
       <c r="U4" t="n">
-        <v>0.3203</v>
+        <v>-0.5407999999999999</v>
       </c>
       <c r="V4" t="n">
-        <v>-0.3943</v>
+        <v>0</v>
       </c>
       <c r="W4" t="n">
-        <v>0.1418</v>
+        <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>-0.5361</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>L. KRATZER</t>
+          <t>A. OBST</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>-1.5573</v>
+        <v>-1.2722</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.9548</v>
+        <v>1.0975</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.6025</v>
+        <v>-2.3697</v>
       </c>
       <c r="G5" t="n">
-        <v>1.356</v>
+        <v>0.3624</v>
       </c>
       <c r="H5" t="n">
-        <v>1.7407</v>
+        <v>0.5666</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.3848</v>
+        <v>-0.2042</v>
       </c>
       <c r="J5" t="n">
-        <v>0.8771</v>
+        <v>3.6577</v>
       </c>
       <c r="K5" t="n">
-        <v>0.8401999999999999</v>
+        <v>1.6504</v>
       </c>
       <c r="L5" t="n">
-        <v>0.0368</v>
+        <v>2.0073</v>
       </c>
       <c r="M5" t="n">
-        <v>0.4789</v>
+        <v>-3.2953</v>
       </c>
       <c r="N5" t="n">
-        <v>0.9005</v>
+        <v>-1.0838</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.4216</v>
+        <v>-2.2116</v>
       </c>
       <c r="P5" t="n">
-        <v>-0.6959</v>
+        <v>-2.3195</v>
       </c>
       <c r="Q5" t="n">
-        <v>-1.1598</v>
+        <v>-3.4793</v>
       </c>
       <c r="R5" t="n">
-        <v>0.4639</v>
+        <v>1.1598</v>
       </c>
       <c r="S5" t="n">
-        <v>-1.1453</v>
+        <v>-0.3872</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.6721</v>
+        <v>-0.1531</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.4731</v>
+        <v>-0.2341</v>
       </c>
       <c r="V5" t="n">
-        <v>-1.0722</v>
+        <v>1.0722</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>1.0722</v>
       </c>
       <c r="X5" t="n">
-        <v>-1.0722</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>J. HOLLATZ</t>
+          <t>K. BALDWIN</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-1.5784</v>
+        <v>-1.4025</v>
       </c>
       <c r="E6" t="n">
-        <v>-1.3684</v>
+        <v>0.3503</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.2099</v>
+        <v>-1.7527</v>
       </c>
       <c r="G6" t="n">
-        <v>-1.4659</v>
+        <v>-1.0229</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.9975000000000001</v>
+        <v>0.2185</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.4684</v>
+        <v>-1.2413</v>
       </c>
       <c r="J6" t="n">
-        <v>-0.4723</v>
+        <v>0.346</v>
       </c>
       <c r="K6" t="n">
-        <v>-0.9005</v>
+        <v>0.2724</v>
       </c>
       <c r="L6" t="n">
-        <v>0.4282</v>
+        <v>0.0736</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.9937</v>
+        <v>-1.3688</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.097</v>
+        <v>-0.0539</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.8966</v>
+        <v>-1.3149</v>
       </c>
       <c r="P6" t="n">
-        <v>1.3917</v>
+        <v>0</v>
       </c>
       <c r="Q6" t="n">
         <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>1.3917</v>
+        <v>0</v>
       </c>
       <c r="S6" t="n">
-        <v>-1.5042</v>
+        <v>0.0147</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.8962</v>
+        <v>-0.1375</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.608</v>
+        <v>0.1522</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>-0.3943</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>0.1418</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>-0.5361</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A. OBST</t>
+          <t>L. KRATZER</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,67 +955,67 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-1.6335</v>
+        <v>-1.4058</v>
       </c>
       <c r="E7" t="n">
-        <v>0.669</v>
+        <v>-0.8369</v>
       </c>
       <c r="F7" t="n">
-        <v>-2.3025</v>
+        <v>-0.5689</v>
       </c>
       <c r="G7" t="n">
-        <v>0.3624</v>
+        <v>1.356</v>
       </c>
       <c r="H7" t="n">
-        <v>0.5666</v>
+        <v>1.7407</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.2042</v>
+        <v>-0.3848</v>
       </c>
       <c r="J7" t="n">
-        <v>3.6577</v>
+        <v>0.8771</v>
       </c>
       <c r="K7" t="n">
-        <v>1.6504</v>
+        <v>0.8401999999999999</v>
       </c>
       <c r="L7" t="n">
-        <v>2.0073</v>
+        <v>0.0368</v>
       </c>
       <c r="M7" t="n">
-        <v>-3.2953</v>
+        <v>0.4789</v>
       </c>
       <c r="N7" t="n">
-        <v>-1.0838</v>
+        <v>0.9005</v>
       </c>
       <c r="O7" t="n">
-        <v>-2.2116</v>
+        <v>-0.4216</v>
       </c>
       <c r="P7" t="n">
-        <v>-2.3195</v>
+        <v>-0.6959</v>
       </c>
       <c r="Q7" t="n">
-        <v>-3.4793</v>
+        <v>-1.1598</v>
       </c>
       <c r="R7" t="n">
-        <v>1.1598</v>
+        <v>0.4639</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.7486</v>
+        <v>-0.9937</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.5816</v>
+        <v>-0.5542</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.1669</v>
+        <v>-0.4395</v>
       </c>
       <c r="V7" t="n">
-        <v>1.0722</v>
+        <v>-1.0722</v>
       </c>
       <c r="W7" t="n">
-        <v>1.0722</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>-1.0722</v>
       </c>
     </row>
     <row r="8">
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-2.2108</v>
+        <v>-2.1608</v>
       </c>
       <c r="E8" t="n">
-        <v>-1.5565</v>
+        <v>-1.6745</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.6543</v>
+        <v>-0.4863</v>
       </c>
       <c r="G8" t="n">
         <v>-3.0449</v>
@@ -1078,13 +1078,13 @@
         <v>0.9278</v>
       </c>
       <c r="S8" t="n">
-        <v>0.4424</v>
+        <v>0.4925</v>
       </c>
       <c r="T8" t="n">
-        <v>0.6449</v>
+        <v>0.5269</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.2025</v>
+        <v>-0.0345</v>
       </c>
       <c r="V8" t="n">
         <v>-0.5361</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-2.3007</v>
+        <v>-2.4358</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.609</v>
+        <v>-0.8449</v>
       </c>
       <c r="F9" t="n">
-        <v>-1.6917</v>
+        <v>-1.5909</v>
       </c>
       <c r="G9" t="n">
         <v>-0.9273</v>
@@ -1156,13 +1156,13 @@
         <v>1.1598</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.3888</v>
+        <v>-0.5239</v>
       </c>
       <c r="T9" t="n">
-        <v>0.0395</v>
+        <v>-0.1964</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.4283</v>
+        <v>-0.3275</v>
       </c>
       <c r="V9" t="n">
         <v>-2.1444</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-4.0573</v>
+        <v>-3.8378</v>
       </c>
       <c r="E10" t="n">
-        <v>-2.5954</v>
+        <v>-2.2416</v>
       </c>
       <c r="F10" t="n">
-        <v>-1.4618</v>
+        <v>-1.5963</v>
       </c>
       <c r="G10" t="n">
         <v>-2.9286</v>
@@ -1234,13 +1234,13 @@
         <v>0.6959</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.5772</v>
+        <v>-0.3578</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.8136</v>
+        <v>-0.4597</v>
       </c>
       <c r="U10" t="n">
-        <v>0.2364</v>
+        <v>0.1019</v>
       </c>
       <c r="V10" t="n">
         <v>1.0722</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-4.6107</v>
+        <v>-4.274</v>
       </c>
       <c r="E11" t="n">
-        <v>-2.215</v>
+        <v>-1.9791</v>
       </c>
       <c r="F11" t="n">
-        <v>-2.3957</v>
+        <v>-2.2949</v>
       </c>
       <c r="G11" t="n">
         <v>-2.2219</v>
@@ -1312,13 +1312,13 @@
         <v>0.9278</v>
       </c>
       <c r="S11" t="n">
-        <v>0.0751</v>
+        <v>0.4118</v>
       </c>
       <c r="T11" t="n">
-        <v>0.0905</v>
+        <v>0.3264</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.0154</v>
+        <v>0.0854</v>
       </c>
       <c r="V11" t="n">
         <v>-1.0722</v>
@@ -1345,10 +1345,10 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-5.1999</v>
+        <v>-4.8893</v>
       </c>
       <c r="E12" t="n">
-        <v>-0.4806</v>
+        <v>-0.17</v>
       </c>
       <c r="F12" t="n">
         <v>-4.7194</v>
@@ -1390,10 +1390,10 @@
         <v>0.4639</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.0747</v>
+        <v>0.2359</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.2082</v>
+        <v>0.1024</v>
       </c>
       <c r="U12" t="n">
         <v>0.1336</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-6.186</v>
+        <v>-5.9091</v>
       </c>
       <c r="E13" t="n">
-        <v>-2.4441</v>
+        <v>-2.1335</v>
       </c>
       <c r="F13" t="n">
-        <v>-3.7419</v>
+        <v>-3.7755</v>
       </c>
       <c r="G13" t="n">
         <v>-3.6943</v>
@@ -1468,13 +1468,13 @@
         <v>1.1598</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.8834</v>
+        <v>-0.6065</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.8136</v>
+        <v>-0.503</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.0698</v>
+        <v>-0.1034</v>
       </c>
       <c r="V13" t="n">
         <v>-1.6083</v>
@@ -1501,19 +1501,19 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>-25.075</v>
+        <v>-24.7019</v>
       </c>
       <c r="E14" t="n">
-        <v>-4.7806</v>
+        <v>-4.407400000000001</v>
       </c>
       <c r="F14" t="n">
-        <v>-20.2943</v>
+        <v>-20.2944</v>
       </c>
       <c r="G14" t="n">
         <v>-14.6142</v>
       </c>
       <c r="H14" t="n">
-        <v>0.8943000000000003</v>
+        <v>0.8943000000000001</v>
       </c>
       <c r="I14" t="n">
         <v>-15.5082</v>
@@ -1546,13 +1546,13 @@
         <v>11.5977</v>
       </c>
       <c r="S14" t="n">
-        <v>-2.693000000000001</v>
+        <v>-2.3196</v>
       </c>
       <c r="T14" t="n">
-        <v>-1.1773</v>
+        <v>-0.8039999999999998</v>
       </c>
       <c r="U14" t="n">
-        <v>-1.5153</v>
+        <v>-1.5155</v>
       </c>
       <c r="V14" t="n">
         <v>-4.2888</v>
@@ -1567,7 +1567,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>L. BIRUTIS</t>
+          <t>S. FRANCISCO</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,73 +1579,73 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>7.2183</v>
+        <v>7.3209</v>
       </c>
       <c r="E15" t="n">
-        <v>4.7117</v>
+        <v>7.7951</v>
       </c>
       <c r="F15" t="n">
-        <v>2.5066</v>
+        <v>-0.4741</v>
       </c>
       <c r="G15" t="n">
-        <v>3.5959</v>
+        <v>7.2744</v>
       </c>
       <c r="H15" t="n">
-        <v>2.9735</v>
+        <v>2.0515</v>
       </c>
       <c r="I15" t="n">
-        <v>0.6224</v>
+        <v>5.2229</v>
       </c>
       <c r="J15" t="n">
-        <v>3.1817</v>
+        <v>8.0253</v>
       </c>
       <c r="K15" t="n">
-        <v>2.9241</v>
+        <v>2.6419</v>
       </c>
       <c r="L15" t="n">
-        <v>0.2576</v>
+        <v>5.3834</v>
       </c>
       <c r="M15" t="n">
-        <v>0.4142</v>
+        <v>-0.7509</v>
       </c>
       <c r="N15" t="n">
-        <v>0.0495</v>
+        <v>-0.5904</v>
       </c>
       <c r="O15" t="n">
-        <v>0.3648</v>
+        <v>-0.1605</v>
       </c>
       <c r="P15" t="n">
-        <v>1.3917</v>
+        <v>-0.232</v>
       </c>
       <c r="Q15" t="n">
-        <v>0</v>
+        <v>-1.1598</v>
       </c>
       <c r="R15" t="n">
-        <v>1.3917</v>
+        <v>0.9278</v>
       </c>
       <c r="S15" t="n">
-        <v>2.0889</v>
+        <v>0.9564</v>
       </c>
       <c r="T15" t="n">
-        <v>1.3882</v>
+        <v>0.3934</v>
       </c>
       <c r="U15" t="n">
-        <v>0.7007</v>
+        <v>0.5629999999999999</v>
       </c>
       <c r="V15" t="n">
-        <v>0.1418</v>
+        <v>-0.6778999999999999</v>
       </c>
       <c r="W15" t="n">
-        <v>0.1418</v>
+        <v>0.5361</v>
       </c>
       <c r="X15" t="n">
-        <v>0</v>
+        <v>-1.214</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>S. FRANCISCO</t>
+          <t>L. BIRUTIS</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,67 +1657,67 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>6.9334</v>
+        <v>6.2411</v>
       </c>
       <c r="E16" t="n">
-        <v>7.4412</v>
+        <v>3.768</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.5077</v>
+        <v>2.473</v>
       </c>
       <c r="G16" t="n">
-        <v>7.2744</v>
+        <v>3.5959</v>
       </c>
       <c r="H16" t="n">
-        <v>2.0515</v>
+        <v>2.9735</v>
       </c>
       <c r="I16" t="n">
-        <v>5.2229</v>
+        <v>0.6224</v>
       </c>
       <c r="J16" t="n">
-        <v>8.0253</v>
+        <v>3.1817</v>
       </c>
       <c r="K16" t="n">
-        <v>2.6419</v>
+        <v>2.9241</v>
       </c>
       <c r="L16" t="n">
-        <v>5.3834</v>
+        <v>0.2576</v>
       </c>
       <c r="M16" t="n">
-        <v>-0.7509</v>
+        <v>0.4142</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.5904</v>
+        <v>0.0495</v>
       </c>
       <c r="O16" t="n">
-        <v>-0.1605</v>
+        <v>0.3648</v>
       </c>
       <c r="P16" t="n">
-        <v>-0.232</v>
+        <v>1.3917</v>
       </c>
       <c r="Q16" t="n">
-        <v>-1.1598</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>0.9278</v>
+        <v>1.3917</v>
       </c>
       <c r="S16" t="n">
-        <v>0.5689</v>
+        <v>1.1116</v>
       </c>
       <c r="T16" t="n">
-        <v>0.0395</v>
+        <v>0.4446</v>
       </c>
       <c r="U16" t="n">
-        <v>0.5294</v>
+        <v>0.6671</v>
       </c>
       <c r="V16" t="n">
-        <v>-0.6778999999999999</v>
+        <v>0.1418</v>
       </c>
       <c r="W16" t="n">
-        <v>0.5361</v>
+        <v>0.1418</v>
       </c>
       <c r="X16" t="n">
-        <v>-1.214</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>5.0799</v>
+        <v>4.2099</v>
       </c>
       <c r="E17" t="n">
-        <v>3.6563</v>
+        <v>2.8306</v>
       </c>
       <c r="F17" t="n">
-        <v>1.4236</v>
+        <v>1.3793</v>
       </c>
       <c r="G17" t="n">
         <v>-0.0384</v>
@@ -1780,13 +1780,13 @@
         <v>1.6237</v>
       </c>
       <c r="S17" t="n">
-        <v>1.8864</v>
+        <v>1.0163</v>
       </c>
       <c r="T17" t="n">
-        <v>1.2388</v>
+        <v>0.4132</v>
       </c>
       <c r="U17" t="n">
-        <v>0.6475</v>
+        <v>0.6032</v>
       </c>
       <c r="V17" t="n">
         <v>1.6083</v>
@@ -1801,7 +1801,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A. BUTKEVICIUS</t>
+          <t>D. SIRVYDIS</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>2.6112</v>
+        <v>3.0743</v>
       </c>
       <c r="E18" t="n">
-        <v>1.0137</v>
+        <v>0.9879</v>
       </c>
       <c r="F18" t="n">
-        <v>1.5975</v>
+        <v>2.0863</v>
       </c>
       <c r="G18" t="n">
-        <v>0.5856</v>
+        <v>2.8254</v>
       </c>
       <c r="H18" t="n">
-        <v>0.5019</v>
+        <v>-0.4201</v>
       </c>
       <c r="I18" t="n">
-        <v>0.0837</v>
+        <v>3.2455</v>
       </c>
       <c r="J18" t="n">
-        <v>1.5365</v>
+        <v>1.8642</v>
       </c>
       <c r="K18" t="n">
-        <v>0.9243</v>
+        <v>-0.6484</v>
       </c>
       <c r="L18" t="n">
-        <v>0.6122</v>
+        <v>2.5127</v>
       </c>
       <c r="M18" t="n">
-        <v>-0.9509</v>
+        <v>0.9611</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.4223</v>
+        <v>0.2283</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.5286</v>
+        <v>0.7328</v>
       </c>
       <c r="P18" t="n">
-        <v>2.0876</v>
+        <v>0.6959</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>-1.1598</v>
       </c>
       <c r="R18" t="n">
-        <v>2.0876</v>
+        <v>1.8556</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.0619</v>
+        <v>0.4835</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.5228</v>
+        <v>0.1417</v>
       </c>
       <c r="U18" t="n">
-        <v>0.4608</v>
+        <v>0.3418</v>
       </c>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>-0.9304</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>0.1418</v>
       </c>
       <c r="X18" t="n">
-        <v>0</v>
+        <v>-1.0722</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>D. SIRVYDIS</t>
+          <t>A. BUTKEVICIUS</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,67 +1891,67 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>2.4617</v>
+        <v>3.0279</v>
       </c>
       <c r="E19" t="n">
-        <v>0.3982</v>
+        <v>1.4856</v>
       </c>
       <c r="F19" t="n">
-        <v>2.0635</v>
+        <v>1.5423</v>
       </c>
       <c r="G19" t="n">
-        <v>2.8254</v>
+        <v>0.5856</v>
       </c>
       <c r="H19" t="n">
-        <v>-0.4201</v>
+        <v>0.5019</v>
       </c>
       <c r="I19" t="n">
-        <v>3.2455</v>
+        <v>0.0837</v>
       </c>
       <c r="J19" t="n">
-        <v>1.8642</v>
+        <v>1.5365</v>
       </c>
       <c r="K19" t="n">
-        <v>-0.6484</v>
+        <v>0.9243</v>
       </c>
       <c r="L19" t="n">
-        <v>2.5127</v>
+        <v>0.6122</v>
       </c>
       <c r="M19" t="n">
-        <v>0.9611</v>
+        <v>-0.9509</v>
       </c>
       <c r="N19" t="n">
-        <v>0.2283</v>
+        <v>-0.4223</v>
       </c>
       <c r="O19" t="n">
-        <v>0.7328</v>
+        <v>-0.5286</v>
       </c>
       <c r="P19" t="n">
-        <v>0.6959</v>
+        <v>2.0876</v>
       </c>
       <c r="Q19" t="n">
-        <v>-1.1598</v>
+        <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>1.8556</v>
+        <v>2.0876</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.1291</v>
+        <v>0.3547</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.4481</v>
+        <v>-0.051</v>
       </c>
       <c r="U19" t="n">
-        <v>0.3189</v>
+        <v>0.4057</v>
       </c>
       <c r="V19" t="n">
-        <v>-0.9304</v>
+        <v>0</v>
       </c>
       <c r="W19" t="n">
-        <v>0.1418</v>
+        <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>-1.0722</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>2.1522</v>
+        <v>2.9042</v>
       </c>
       <c r="E20" t="n">
-        <v>1.299</v>
+        <v>1.5349</v>
       </c>
       <c r="F20" t="n">
-        <v>0.8531</v>
+        <v>1.3693</v>
       </c>
       <c r="G20" t="n">
         <v>2.8061</v>
@@ -2014,13 +2014,13 @@
         <v>1.8556</v>
       </c>
       <c r="S20" t="n">
-        <v>-1.1747</v>
+        <v>-0.4226</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.5228</v>
+        <v>-0.2869</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.6519</v>
+        <v>-0.1357</v>
       </c>
       <c r="V20" t="n">
         <v>2.1444</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>0.8512</v>
+        <v>1.3731</v>
       </c>
       <c r="E21" t="n">
-        <v>0.5943000000000001</v>
+        <v>0.9481000000000001</v>
       </c>
       <c r="F21" t="n">
-        <v>0.2569</v>
+        <v>0.4249</v>
       </c>
       <c r="G21" t="n">
         <v>0.0641</v>
@@ -2092,13 +2092,13 @@
         <v>1.6237</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.749</v>
+        <v>-0.2271</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.5228</v>
+        <v>-0.1689</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.2262</v>
+        <v>-0.0582</v>
       </c>
       <c r="V21" t="n">
         <v>1.0722</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>0.6975</v>
+        <v>1.1915</v>
       </c>
       <c r="E22" t="n">
-        <v>1.7751</v>
+        <v>2.011</v>
       </c>
       <c r="F22" t="n">
-        <v>-1.0776</v>
+        <v>-0.8195</v>
       </c>
       <c r="G22" t="n">
         <v>0.79</v>
@@ -2170,13 +2170,13 @@
         <v>0.6959</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.1647</v>
+        <v>0.3293</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.0747</v>
+        <v>0.1612</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.0901</v>
+        <v>0.168</v>
       </c>
       <c r="V22" t="n">
         <v>0.5361</v>
@@ -2191,7 +2191,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>M. WRIGHT</t>
+          <t>N. WILLIAMS-GOSS</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,73 +2203,73 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>0.3457</v>
+        <v>0.0401</v>
       </c>
       <c r="E23" t="n">
-        <v>1.6676</v>
+        <v>-0.716</v>
       </c>
       <c r="F23" t="n">
-        <v>-1.3219</v>
+        <v>0.756</v>
       </c>
       <c r="G23" t="n">
-        <v>-0.4751</v>
+        <v>0.6327</v>
       </c>
       <c r="H23" t="n">
-        <v>0.1103</v>
+        <v>-1.7731</v>
       </c>
       <c r="I23" t="n">
-        <v>-0.5855</v>
+        <v>2.4058</v>
       </c>
       <c r="J23" t="n">
-        <v>1.1049</v>
+        <v>0.8367</v>
       </c>
       <c r="K23" t="n">
-        <v>0.8472</v>
+        <v>-1.5188</v>
       </c>
       <c r="L23" t="n">
-        <v>0.2576</v>
+        <v>2.3555</v>
       </c>
       <c r="M23" t="n">
-        <v>-1.58</v>
+        <v>-0.204</v>
       </c>
       <c r="N23" t="n">
-        <v>-0.7369</v>
+        <v>-0.2543</v>
       </c>
       <c r="O23" t="n">
-        <v>-0.8431</v>
+        <v>0.0502</v>
       </c>
       <c r="P23" t="n">
-        <v>-0.6959</v>
+        <v>-0.232</v>
       </c>
       <c r="Q23" t="n">
-        <v>-2.3195</v>
+        <v>-1.1598</v>
       </c>
       <c r="R23" t="n">
-        <v>1.6237</v>
+        <v>0.9278</v>
       </c>
       <c r="S23" t="n">
-        <v>1.1224</v>
+        <v>-0.3607</v>
       </c>
       <c r="T23" t="n">
-        <v>1.274</v>
+        <v>-0.393</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.1516</v>
+        <v>0.0323</v>
       </c>
       <c r="V23" t="n">
-        <v>0.3943</v>
+        <v>0</v>
       </c>
       <c r="W23" t="n">
-        <v>1.6083</v>
+        <v>0</v>
       </c>
       <c r="X23" t="n">
-        <v>-1.214</v>
+        <v>0</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>N. WILLIAMS-GOSS</t>
+          <t>M. WRIGHT</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2281,67 +2281,67 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-0.7735</v>
+        <v>-0.3334</v>
       </c>
       <c r="E24" t="n">
-        <v>-1.0698</v>
+        <v>0.842</v>
       </c>
       <c r="F24" t="n">
-        <v>0.2963</v>
+        <v>-1.1754</v>
       </c>
       <c r="G24" t="n">
-        <v>0.6327</v>
+        <v>-0.4751</v>
       </c>
       <c r="H24" t="n">
-        <v>-1.7731</v>
+        <v>0.1103</v>
       </c>
       <c r="I24" t="n">
-        <v>2.4058</v>
+        <v>-0.5855</v>
       </c>
       <c r="J24" t="n">
-        <v>0.8367</v>
+        <v>1.1049</v>
       </c>
       <c r="K24" t="n">
-        <v>-1.5188</v>
+        <v>0.8472</v>
       </c>
       <c r="L24" t="n">
-        <v>2.3555</v>
+        <v>0.2576</v>
       </c>
       <c r="M24" t="n">
-        <v>-0.204</v>
+        <v>-1.58</v>
       </c>
       <c r="N24" t="n">
-        <v>-0.2543</v>
+        <v>-0.7369</v>
       </c>
       <c r="O24" t="n">
-        <v>0.0502</v>
+        <v>-0.8431</v>
       </c>
       <c r="P24" t="n">
-        <v>-0.232</v>
+        <v>-0.6959</v>
       </c>
       <c r="Q24" t="n">
-        <v>-1.1598</v>
+        <v>-2.3195</v>
       </c>
       <c r="R24" t="n">
-        <v>0.9278</v>
+        <v>1.6237</v>
       </c>
       <c r="S24" t="n">
-        <v>-1.1742</v>
+        <v>0.4433</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.7468</v>
+        <v>0.4483</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.4274</v>
+        <v>-0.005</v>
       </c>
       <c r="V24" t="n">
-        <v>0</v>
+        <v>0.3943</v>
       </c>
       <c r="W24" t="n">
-        <v>0</v>
+        <v>1.6083</v>
       </c>
       <c r="X24" t="n">
-        <v>0</v>
+        <v>-1.214</v>
       </c>
     </row>
     <row r="25">
@@ -2359,10 +2359,10 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-1.1939</v>
+        <v>-1.076</v>
       </c>
       <c r="E25" t="n">
-        <v>-0.5217000000000001</v>
+        <v>-0.4038</v>
       </c>
       <c r="F25" t="n">
         <v>-0.6722</v>
@@ -2404,10 +2404,10 @@
         <v>0.232</v>
       </c>
       <c r="S25" t="n">
-        <v>-0.0747</v>
+        <v>0.0433</v>
       </c>
       <c r="T25" t="n">
-        <v>-0.0747</v>
+        <v>0.0433</v>
       </c>
       <c r="U25" t="n">
         <v>0</v>
@@ -2437,13 +2437,13 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>-1.3085</v>
+        <v>-1.3256</v>
       </c>
       <c r="E26" t="n">
-        <v>-0.6712</v>
+        <v>-0.7891</v>
       </c>
       <c r="F26" t="n">
-        <v>-0.6373</v>
+        <v>-0.5365</v>
       </c>
       <c r="G26" t="n">
         <v>-2.0953</v>
@@ -2482,13 +2482,13 @@
         <v>0.232</v>
       </c>
       <c r="S26" t="n">
-        <v>0.5548</v>
+        <v>0.5377</v>
       </c>
       <c r="T26" t="n">
-        <v>0.4876</v>
+        <v>0.3697</v>
       </c>
       <c r="U26" t="n">
-        <v>0.0672</v>
+        <v>0.168</v>
       </c>
       <c r="V26" t="n">
         <v>0</v>
@@ -2515,19 +2515,19 @@
         <v>1</v>
       </c>
       <c r="D27" t="n">
-        <v>25.07520000000001</v>
+        <v>26.648</v>
       </c>
       <c r="E27" t="n">
-        <v>20.2944</v>
+        <v>20.2943</v>
       </c>
       <c r="F27" t="n">
-        <v>4.780799999999999</v>
+        <v>6.353400000000001</v>
       </c>
       <c r="G27" t="n">
         <v>14.6142</v>
       </c>
       <c r="H27" t="n">
-        <v>-0.8941999999999993</v>
+        <v>-0.8941999999999998</v>
       </c>
       <c r="I27" t="n">
         <v>15.5083</v>
@@ -2551,7 +2551,7 @@
         <v>-2.3916</v>
       </c>
       <c r="P27" t="n">
-        <v>3.479300000000001</v>
+        <v>3.4793</v>
       </c>
       <c r="Q27" t="n">
         <v>-11.5978</v>
@@ -2560,13 +2560,13 @@
         <v>15.0771</v>
       </c>
       <c r="S27" t="n">
-        <v>2.6931</v>
+        <v>4.2657</v>
       </c>
       <c r="T27" t="n">
-        <v>1.5154</v>
+        <v>1.5156</v>
       </c>
       <c r="U27" t="n">
-        <v>1.1773</v>
+        <v>2.7502</v>
       </c>
       <c r="V27" t="n">
         <v>4.2888</v>
